--- a/Assets/Config/GameBalance.xlsx
+++ b/Assets/Config/GameBalance.xlsx
@@ -10,26 +10,18 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2C9912A-5ED9-40A9-AC80-C87875D10C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
     <sheet name="Marble" sheetId="2" r:id="rId2"/>
     <sheet name="Campaign" sheetId="3" r:id="rId3"/>
-    <sheet name="Board" sheetId="4" r:id="rId4"/>
     <sheet name="Stages" sheetId="5" r:id="rId5"/>
-    <sheet name="Devices" sheetId="6" r:id="rId6"/>
-    <sheet name="Drugs" sheetId="7" r:id="rId7"/>
-    <sheet name="Zones" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Board!$A$1:$C$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Campaign!$A$1:$C$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Devices!$A$1:$G$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Drugs!$A$1:$F$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Marble!$A$1:$C$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Stages!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Zones!$A$1:$J$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Marble!$A$1:$C$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Stages!$A$1:$E$7</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -120,362 +112,10 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Marble ECS</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>表内唯一正整数编号；Zones 限定 1..99999。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>显示名称，1..80 个字符。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>购买价格，正整数金币。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>装置：倍分钉固定 2、Rush 钉为 1。区域：终点得分倍率。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>碰撞 Enter 后血珠的 Rush 概率加成；0.08 表示增加 8 个百分点。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>装置钉半径，米。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0500-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>新游戏赠送数量。</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Marble ECS</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>表内唯一正整数编号；Zones 限定 1..99999。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>显示名称，1..80 个字符。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>购买价格，正整数金币。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>药物对恢复系数的乘数；不同用药乘法叠加，最终系数限制在 0..1。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>药物作用于新发射血珠的持续时间，秒；场内血珠保留发射快照。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>新游戏赠送数量。</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Marble ECS</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>表内唯一正整数编号；Zones 限定 1..99999。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>显示名称，1..80 个字符。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>0=普通得分；1=赌博待定分数；2=落空回收。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>装置：倍分钉固定 2、Rush 钉为 1。区域：终点得分倍率。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>该终点是否进行 Rush 概率判定；落空区必须 FALSE。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>同一步多个终点按优先级降序，其次按 Id 升序选唯一一个。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>终点区域中心局部 X 坐标，米。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>终点区域中心局部 Z 坐标，米；位于布置区下方。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>盘面/分区的局部 X 宽度，米。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="宋体"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>终点区域局部 Z 深度，米。</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="169">
   <si>
-    <t>血珠弹珠机：首版可调数值表</t>
+    <t>血珠弹珠机：基础数值表</t>
   </si>
   <si>
     <t>策划直接修改本工作簿。保存并切回 Unity 后自动导入；或 Marbles ECS &gt; Import Game Balance Excel。</t>
@@ -496,10 +136,10 @@
     <t>战役累计目标只改 Stages.TargetScore；Marble.TargetScore 供旧独立模拟使用。</t>
   </si>
   <si>
-    <t>仅两种钉子（x2 与 Rush+）；两档药物只影响碰撞恢复系数。完整规则与初版调参说明见 Docs/Balance.md。</t>
-  </si>
-  <si>
-    <t>本文件独立于 PachinkoECSDesign_3D.xlsx：设计规格表保留，运行数值从这里导入。</t>
+    <t>属性、装置和药物统一在 Resources/GameContent.json 配置，本表不再保存这些重复数值。完整调参说明见 Docs/Balance.md。</t>
+  </si>
+  <si>
+    <t>本表只导入基础运行与战役参数；盘面在场景配置。规范工作簿需显式导入才会更新 GameContent.json。</t>
   </si>
   <si>
     <t>Field</t>
@@ -1378,8 +1018,10 @@
       </c>
     </row>
     <row r="4" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Marble / Campaign：仅编辑 Value 列。其他表每行一条配置，鼠标悬停表头查看字段解释。</t>
+        </is>
       </c>
     </row>
     <row r="5" spans="1:1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
@@ -1415,7 +1057,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -1478,39 +1120,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.119999997317791</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.2199999988079071</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.10000000149011611</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>26</v>
@@ -1522,39 +1131,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="3">
-        <v>10</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="4">
-        <v>0.06</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="3">
-        <v>1</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>34</v>
@@ -1566,28 +1142,6 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B14" s="3">
-        <v>5</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B15" s="4">
-        <v>1</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>40</v>
@@ -1599,17 +1153,6 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="4">
-        <v>45</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>44</v>
@@ -1643,50 +1186,6 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="4">
-        <v>5</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="3">
-        <v>20</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B23" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="3">
-        <v>0.44999998807907099</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>58</v>
@@ -1743,13 +1242,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C29" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:C30" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Boolean required" error="Use TRUE or FALSE." sqref="B23" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1786,17 +1280,6 @@
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>72</v>
@@ -1852,28 +1335,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="3">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>86</v>
@@ -1887,331 +1348,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:C11" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="92" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="3">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B3" s="4">
-        <v>16</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.34999999403953552</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="4">
-        <v>22</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.85000002384185791</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="4">
-        <v>0.30000001192092901</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="3">
-        <v>-4</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="4">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="3">
-        <v>-4.5</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" s="4">
-        <v>5</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B12" s="3">
-        <v>0.15000000596046451</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0.69999998807907104</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" s="4">
-        <v>0</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="3">
-        <v>6.5</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" s="4">
-        <v>0.34999999403953552</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="3">
-        <v>10</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" s="4">
-        <v>3.7999999523162842</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" s="3">
-        <v>4</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B21" s="4">
-        <v>1.666666753590107E-2</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" s="3">
-        <v>4</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="4">
-        <v>5</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" s="3">
-        <v>7</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="4">
-        <v>0.12999999523162839</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" s="3">
-        <v>1.1499999761581421</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="4">
-        <v>1.6499999761581421</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" s="3">
-        <v>3.7000000476837158</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:C28" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2351,380 +1487,4 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="7" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C2" s="3">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3">
-        <v>2</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.1800000071525574</v>
-      </c>
-      <c r="G2" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="4">
-        <v>20</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0.08</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0.1800000071525574</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="24" customWidth="1"/>
-    <col min="5" max="6" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C2" s="3">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="E2" s="3">
-        <v>12</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" s="4">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0.64999997615814209</v>
-      </c>
-      <c r="E3" s="4">
-        <v>12</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F3" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="18" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="3">
-        <v>-6.8000001907348633</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1.799999952316284</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1.6000000238418579</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" s="4">
-        <v>100</v>
-      </c>
-      <c r="G3" s="4">
-        <v>-2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>-6.8000001907348633</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1.799999952316284</v>
-      </c>
-      <c r="J3" s="4">
-        <v>1.6000000238418579</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>100</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>-6.8000001907348633</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1.799999952316284</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1.6000000238418579</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.5</v>
-      </c>
-      <c r="E5" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4">
-        <v>100</v>
-      </c>
-      <c r="G5" s="4">
-        <v>2</v>
-      </c>
-      <c r="H5" s="4">
-        <v>-6.8000001907348633</v>
-      </c>
-      <c r="I5" s="4">
-        <v>1.799999952316284</v>
-      </c>
-      <c r="J5" s="4">
-        <v>1.6000000238418579</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="3">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>4</v>
-      </c>
-      <c r="H6" s="3">
-        <v>-6.8000001907348633</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1.799999952316284</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1.6000000238418579</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J6" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" errorTitle="Boolean required" error="Use TRUE or FALSE." sqref="E2:E6" xr:uid="{00000000-0002-0000-0700-000000000000}">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Assets/Config/GameBalance.xlsx
+++ b/Assets/Config/GameBalance.xlsx
@@ -728,17 +728,6 @@
         <x:v>30</x:v>
       </x:c>
     </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B25" s="4">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C25" s="4" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
     <x:row r="26">
       <x:c r="A26" s="3" t="s">
         <x:v>33</x:v>
@@ -863,17 +852,6 @@
         <x:v>49</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="3" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="B8" s="3">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
     <x:row r="11">
       <x:c r="A11" s="4" t="s">
         <x:v>52</x:v>

--- a/Assets/Config/GameBalance.xlsx
+++ b/Assets/Config/GameBalance.xlsx
@@ -617,7 +617,7 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>最高发射频率的间隔（秒）；当前约 6.67 次/秒。</t>
+          <t>长按空格加速完成后的连发间隔（秒）；默认 0.15 秒，约 6.67 次/秒。</t>
         </is>
       </c>
     </row>
@@ -633,6 +633,21 @@
       <c r="C14" s="10" t="inlineStr">
         <is>
           <t>长按空格从 0 加速至最高发射频率的时间（秒）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>MaxFireIntervalSeconds</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>点按的最短发射间隔（秒）；超速输入直接丢弃。数值越小允许点按越快，与长按间隔独立。</t>
         </is>
       </c>
     </row>
